--- a/etf_holdings/2026-10-13_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-13_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3393,52 +3393,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1665000</v>
+      </c>
       <c r="K49" t="n">
-        <v>359000</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>967000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-698,000</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3448,60 +3466,56 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>170000</v>
+        <v>700000</v>
       </c>
       <c r="K50" t="n">
-        <v>176000</v>
+        <v>5000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>-695,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3516,55 +3530,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>659000</v>
+        <v>529000</v>
       </c>
       <c r="K51" t="n">
-        <v>675000</v>
+        <v>609000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,55 +3593,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1204000</v>
+        <v>786000</v>
       </c>
       <c r="K52" t="n">
-        <v>1227000</v>
+        <v>846000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3642,39 +3656,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>196000</v>
+        <v>169000</v>
       </c>
       <c r="K53" t="n">
-        <v>201000</v>
+        <v>174000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3683,14 +3697,14 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,55 +3719,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>422000</v>
+        <v>810000</v>
       </c>
       <c r="K54" t="n">
-        <v>424000</v>
+        <v>829000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3763,60 +3777,60 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>508000</v>
+        <v>19000</v>
       </c>
       <c r="K55" t="n">
-        <v>520000</v>
+        <v>11000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3831,55 +3845,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6.18%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>465000</v>
+        <v>214000</v>
       </c>
       <c r="K56" t="n">
-        <v>475000</v>
+        <v>222000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,32 +3903,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3923,26 +3937,26 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>155000</v>
+        <v>1345000</v>
       </c>
       <c r="K57" t="n">
-        <v>158000</v>
+        <v>1333000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3957,55 +3971,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>871000</v>
+        <v>184000</v>
       </c>
       <c r="K58" t="n">
-        <v>894000</v>
+        <v>185000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4015,60 +4029,60 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>261000</v>
+        <v>59000</v>
       </c>
       <c r="K59" t="n">
-        <v>267000</v>
+        <v>56000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4083,39 +4097,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>63000</v>
+        <v>22000</v>
       </c>
       <c r="K60" t="n">
-        <v>64000</v>
+        <v>23000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4124,14 +4138,14 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4146,55 +4160,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>844013</v>
+        <v>199000</v>
       </c>
       <c r="K61" t="n">
-        <v>860013</v>
+        <v>206000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4209,55 +4223,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>164000</v>
+        <v>37000</v>
       </c>
       <c r="K62" t="n">
-        <v>194000</v>
+        <v>40000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4267,60 +4281,60 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>33000</v>
+        <v>607000</v>
       </c>
       <c r="K63" t="n">
-        <v>34000</v>
+        <v>577000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4335,55 +4349,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>250000</v>
+        <v>89000</v>
       </c>
       <c r="K64" t="n">
-        <v>255000</v>
+        <v>96000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4398,55 +4412,55 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>99952</v>
+        <v>274000</v>
       </c>
       <c r="K65" t="n">
-        <v>149952</v>
+        <v>296000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4461,55 +4475,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>250000</v>
+        <v>130000</v>
       </c>
       <c r="K66" t="n">
-        <v>256000</v>
+        <v>134000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4524,55 +4538,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>373000</v>
+        <v>41000</v>
       </c>
       <c r="K67" t="n">
-        <v>379000</v>
+        <v>46000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4587,27 +4601,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4616,26 +4630,26 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>113000</v>
+        <v>191000</v>
       </c>
       <c r="K68" t="n">
-        <v>133000</v>
+        <v>204000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4650,27 +4664,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>4.68%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4679,26 +4693,26 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>51000</v>
+        <v>446000</v>
       </c>
       <c r="K69" t="n">
-        <v>52000</v>
+        <v>464000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4713,55 +4727,55 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>429675</v>
+        <v>198000</v>
       </c>
       <c r="K70" t="n">
-        <v>440675</v>
+        <v>214000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4776,55 +4790,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>968000</v>
+        <v>108000</v>
       </c>
       <c r="K71" t="n">
-        <v>986000</v>
+        <v>116000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4839,27 +4853,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4868,26 +4882,26 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1957000</v>
+        <v>58000</v>
       </c>
       <c r="K72" t="n">
-        <v>1991000</v>
+        <v>62000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-11_00992A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4902,55 +4916,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1665000</v>
+        <v>13000</v>
       </c>
       <c r="K73" t="n">
-        <v>967000</v>
+        <v>11000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-698,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-11_00990A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4960,56 +4974,60 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
       <c r="J74" t="n">
-        <v>700000</v>
+        <v>240000</v>
       </c>
       <c r="K74" t="n">
-        <v>5000</v>
+        <v>248000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-695,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-10-11_00405A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5024,48 +5042,48 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>529000</v>
+        <v>395000</v>
       </c>
       <c r="K75" t="n">
-        <v>609000</v>
+        <v>411000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-10-11_00405A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -5087,43 +5105,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>786000</v>
+        <v>114000</v>
       </c>
       <c r="K76" t="n">
-        <v>846000</v>
+        <v>121000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5145,48 +5163,48 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>169000</v>
+        <v>79000</v>
       </c>
       <c r="K77" t="n">
-        <v>174000</v>
+        <v>76000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5213,39 +5231,39 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>810000</v>
+        <v>368000</v>
       </c>
       <c r="K78" t="n">
-        <v>829000</v>
+        <v>387000</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -5271,48 +5289,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>19000</v>
+        <v>1023000</v>
       </c>
       <c r="K79" t="n">
-        <v>11000</v>
+        <v>1092000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5339,27 +5357,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,14 +5386,14 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>214000</v>
+        <v>47000</v>
       </c>
       <c r="K80" t="n">
-        <v>222000</v>
+        <v>51000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5397,48 +5415,48 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1345000</v>
+        <v>172000</v>
       </c>
       <c r="K81" t="n">
-        <v>1333000</v>
+        <v>183000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5465,39 +5483,39 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>184000</v>
+        <v>280000</v>
       </c>
       <c r="K82" t="n">
-        <v>185000</v>
+        <v>281000</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -5513,133 +5531,97 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.15%</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>59000</v>
-      </c>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-3,000</t>
-        </is>
-      </c>
+        <v>469000</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>22000</v>
-      </c>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+        <v>3054000</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5654,55 +5636,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>199000</v>
+        <v>39000</v>
       </c>
       <c r="K85" t="n">
-        <v>206000</v>
+        <v>51000</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5712,60 +5694,60 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>37000</v>
+        <v>137000</v>
       </c>
       <c r="K86" t="n">
-        <v>40000</v>
+        <v>97000</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>-40,000</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5775,1527 +5757,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>607000</v>
+        <v>669000</v>
       </c>
       <c r="K87" t="n">
-        <v>577000</v>
+        <v>804000</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>135,000</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0.55%</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>89000</v>
-      </c>
-      <c r="K88" t="n">
-        <v>96000</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0.55%</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>274000</v>
-      </c>
-      <c r="K89" t="n">
-        <v>296000</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>22,000</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0.72%</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>130000</v>
-      </c>
-      <c r="K90" t="n">
-        <v>134000</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>41000</v>
-      </c>
-      <c r="K91" t="n">
-        <v>46000</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>191000</v>
-      </c>
-      <c r="K92" t="n">
-        <v>204000</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>4.68%</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>4.73%</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>446000</v>
-      </c>
-      <c r="K93" t="n">
-        <v>464000</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>18,000</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>198000</v>
-      </c>
-      <c r="K94" t="n">
-        <v>214000</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>16,000</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K95" t="n">
-        <v>116000</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K96" t="n">
-        <v>62000</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>13000</v>
-      </c>
-      <c r="K97" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>1.82%</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>240000</v>
-      </c>
-      <c r="K98" t="n">
-        <v>248000</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2.30%</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>395000</v>
-      </c>
-      <c r="K99" t="n">
-        <v>411000</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>16,000</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>114000</v>
-      </c>
-      <c r="K100" t="n">
-        <v>121000</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>4.48%</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>+0.31%</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>79000</v>
-      </c>
-      <c r="K101" t="n">
-        <v>76000</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>-3,000</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>368000</v>
-      </c>
-      <c r="K102" t="n">
-        <v>387000</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>19,000</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>1023000</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1092000</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>69,000</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>1.10%</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>1.11%</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>47000</v>
-      </c>
-      <c r="K104" t="n">
-        <v>51000</v>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>尖點</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>尖點</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>0.97%</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>172000</v>
-      </c>
-      <c r="K105" t="n">
-        <v>183000</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>3.96%</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>3.89%</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>280000</v>
-      </c>
-      <c r="K106" t="n">
-        <v>281000</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="n">
-        <v>469000</v>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="n">
-        <v>3054000</v>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>+0.35%</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>39000</v>
-      </c>
-      <c r="K109" t="n">
-        <v>51000</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>2.53%</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-1.22%</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>137000</v>
-      </c>
-      <c r="K110" t="n">
-        <v>97000</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>-40,000</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>669000</v>
-      </c>
-      <c r="K111" t="n">
-        <v>804000</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>135,000</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
         <is>
           <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-10-13_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-13_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3393,70 +3393,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>1665000</v>
-      </c>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>967000</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-698,000</t>
-        </is>
-      </c>
+        <v>359000</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-11_00990A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3466,56 +3448,60 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
       <c r="J50" t="n">
-        <v>700000</v>
+        <v>170000</v>
       </c>
       <c r="K50" t="n">
-        <v>5000</v>
+        <v>176000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-695,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-11_00405A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3530,55 +3516,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>529000</v>
+        <v>659000</v>
       </c>
       <c r="K51" t="n">
-        <v>609000</v>
+        <v>675000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-11_00405A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,55 +3579,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>786000</v>
+        <v>1204000</v>
       </c>
       <c r="K52" t="n">
-        <v>846000</v>
+        <v>1227000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3656,39 +3642,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>169000</v>
+        <v>196000</v>
       </c>
       <c r="K53" t="n">
-        <v>174000</v>
+        <v>201000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3697,14 +3683,14 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3719,55 +3705,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>810000</v>
+        <v>422000</v>
       </c>
       <c r="K54" t="n">
-        <v>829000</v>
+        <v>424000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3777,60 +3763,60 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>19000</v>
+        <v>508000</v>
       </c>
       <c r="K55" t="n">
-        <v>11000</v>
+        <v>520000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3845,55 +3831,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>6.18%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>6.32%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>214000</v>
+        <v>465000</v>
       </c>
       <c r="K56" t="n">
-        <v>222000</v>
+        <v>475000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3903,32 +3889,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3937,26 +3923,26 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1345000</v>
+        <v>155000</v>
       </c>
       <c r="K57" t="n">
-        <v>1333000</v>
+        <v>158000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3971,55 +3957,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>184000</v>
+        <v>871000</v>
       </c>
       <c r="K58" t="n">
-        <v>185000</v>
+        <v>894000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4029,60 +4015,60 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>59000</v>
+        <v>261000</v>
       </c>
       <c r="K59" t="n">
-        <v>56000</v>
+        <v>267000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4097,39 +4083,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>22000</v>
+        <v>63000</v>
       </c>
       <c r="K60" t="n">
-        <v>23000</v>
+        <v>64000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4138,14 +4124,14 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4160,55 +4146,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>199000</v>
+        <v>844013</v>
       </c>
       <c r="K61" t="n">
-        <v>206000</v>
+        <v>860013</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4223,55 +4209,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>37000</v>
+        <v>164000</v>
       </c>
       <c r="K62" t="n">
-        <v>40000</v>
+        <v>194000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4281,60 +4267,60 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>607000</v>
+        <v>33000</v>
       </c>
       <c r="K63" t="n">
-        <v>577000</v>
+        <v>34000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4349,55 +4335,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>89000</v>
+        <v>250000</v>
       </c>
       <c r="K64" t="n">
-        <v>96000</v>
+        <v>255000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4412,55 +4398,55 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>274000</v>
+        <v>99952</v>
       </c>
       <c r="K65" t="n">
-        <v>296000</v>
+        <v>149952</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4475,55 +4461,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>130000</v>
+        <v>250000</v>
       </c>
       <c r="K66" t="n">
-        <v>134000</v>
+        <v>256000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4538,55 +4524,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>41000</v>
+        <v>373000</v>
       </c>
       <c r="K67" t="n">
-        <v>46000</v>
+        <v>379000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4601,27 +4587,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4630,26 +4616,26 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>191000</v>
+        <v>113000</v>
       </c>
       <c r="K68" t="n">
-        <v>204000</v>
+        <v>133000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4664,27 +4650,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4693,26 +4679,26 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>446000</v>
+        <v>51000</v>
       </c>
       <c r="K69" t="n">
-        <v>464000</v>
+        <v>52000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4727,55 +4713,55 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>198000</v>
+        <v>429675</v>
       </c>
       <c r="K70" t="n">
-        <v>214000</v>
+        <v>440675</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4790,55 +4776,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>108000</v>
+        <v>968000</v>
       </c>
       <c r="K71" t="n">
-        <v>116000</v>
+        <v>986000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4853,27 +4839,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4882,26 +4868,26 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>58000</v>
+        <v>1957000</v>
       </c>
       <c r="K72" t="n">
-        <v>62000</v>
+        <v>1991000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4916,55 +4902,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>13000</v>
+        <v>1665000</v>
       </c>
       <c r="K73" t="n">
-        <v>11000</v>
+        <v>967000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-698,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4974,60 +4960,56 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.82%</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>240000</v>
+        <v>700000</v>
       </c>
       <c r="K74" t="n">
-        <v>248000</v>
+        <v>5000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-695,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5042,48 +5024,48 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>395000</v>
+        <v>529000</v>
       </c>
       <c r="K75" t="n">
-        <v>411000</v>
+        <v>609000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+          <t>2026-10-11_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -5105,43 +5087,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>114000</v>
+        <v>786000</v>
       </c>
       <c r="K76" t="n">
-        <v>121000</v>
+        <v>846000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5163,48 +5145,48 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>79000</v>
+        <v>169000</v>
       </c>
       <c r="K77" t="n">
-        <v>76000</v>
+        <v>174000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5231,39 +5213,39 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>368000</v>
+        <v>810000</v>
       </c>
       <c r="K78" t="n">
-        <v>387000</v>
+        <v>829000</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -5289,48 +5271,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1023000</v>
+        <v>19000</v>
       </c>
       <c r="K79" t="n">
-        <v>1092000</v>
+        <v>11000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5357,27 +5339,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5386,14 +5368,14 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>47000</v>
+        <v>214000</v>
       </c>
       <c r="K80" t="n">
-        <v>51000</v>
+        <v>222000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5415,48 +5397,48 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>172000</v>
+        <v>1345000</v>
       </c>
       <c r="K81" t="n">
-        <v>183000</v>
+        <v>1333000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5483,39 +5465,39 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>280000</v>
+        <v>184000</v>
       </c>
       <c r="K82" t="n">
-        <v>281000</v>
+        <v>185000</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -5531,97 +5513,133 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>59000</v>
+      </c>
       <c r="K83" t="n">
-        <v>469000</v>
-      </c>
-      <c r="L83" t="inlineStr"/>
+        <v>56000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>22000</v>
+      </c>
       <c r="K84" t="n">
-        <v>3054000</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
+        <v>23000</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5636,55 +5654,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>39000</v>
+        <v>199000</v>
       </c>
       <c r="K85" t="n">
-        <v>51000</v>
+        <v>206000</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5694,114 +5712,1590 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>137000</v>
+        <v>37000</v>
       </c>
       <c r="K86" t="n">
-        <v>97000</v>
+        <v>40000</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-40,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>607000</v>
+      </c>
+      <c r="K87" t="n">
+        <v>577000</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>89000</v>
+      </c>
+      <c r="K88" t="n">
+        <v>96000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>274000</v>
+      </c>
+      <c r="K89" t="n">
+        <v>296000</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>130000</v>
+      </c>
+      <c r="K90" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K91" t="n">
+        <v>46000</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>191000</v>
+      </c>
+      <c r="K92" t="n">
+        <v>204000</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>4.68%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>4.73%</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>446000</v>
+      </c>
+      <c r="K93" t="n">
+        <v>464000</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>198000</v>
+      </c>
+      <c r="K94" t="n">
+        <v>214000</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>108000</v>
+      </c>
+      <c r="K95" t="n">
+        <v>116000</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K96" t="n">
+        <v>62000</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>13000</v>
+      </c>
+      <c r="K97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K98" t="n">
+        <v>248000</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>395000</v>
+      </c>
+      <c r="K99" t="n">
+        <v>411000</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>114000</v>
+      </c>
+      <c r="K100" t="n">
+        <v>121000</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K101" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>368000</v>
+      </c>
+      <c r="K102" t="n">
+        <v>387000</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>19,000</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>1023000</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1092000</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>47000</v>
+      </c>
+      <c r="K104" t="n">
+        <v>51000</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>尖點</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>尖點</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>172000</v>
+      </c>
+      <c r="K105" t="n">
+        <v>183000</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>280000</v>
+      </c>
+      <c r="K106" t="n">
+        <v>281000</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-11_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>469000</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>3054000</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K109" t="n">
+        <v>51000</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>137000</v>
+      </c>
+      <c r="K110" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-11_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>6278</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>台表科</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>台表科</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>0.71%</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>+0.17%</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J111" t="n">
         <v>669000</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K111" t="n">
         <v>804000</v>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>135,000</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>2026-10-11_00400A_full_holdings.xlsx</t>
         </is>
